--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="214">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,6 +391,9 @@
     <t>Performer1.typeCode</t>
   </si>
   <si>
+    <t>PRF pour performer (Exécutant)</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-xServiceEventPerformer</t>
   </si>
   <si>
@@ -401,6 +404,9 @@
 </t>
   </si>
   <si>
+    <t>Rôle fonctionnel</t>
+  </si>
+  <si>
     <t>Performer1.time</t>
   </si>
   <si>
@@ -408,11 +414,267 @@
 </t>
   </si>
   <si>
+    <t>Date et heure de participation</t>
+  </si>
+  <si>
     <t>Performer1.assignedEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
+  </si>
+  <si>
+    <t>Exécutant</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.nullFlavor</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.realmCode</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId.root</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.typeId.extension</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.templateId</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>ASSIGNED</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-RoleClassAssignedEntity</t>
+  </si>
+  <si>
+    <t>AssignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IdentifiedBy
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+  </si>
+  <si>
+    <t>AssignedEntity.code</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.addr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.addr</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.telecom</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.sdtcPatient.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient.id</t>
   </si>
 </sst>
 </file>
@@ -714,11 +976,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.94921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.94921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -742,13 +1004,13 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.38671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1292,7 +1554,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1393,7 +1655,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1496,7 +1758,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1918,7 +2180,9 @@
       <c r="K12" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1949,7 +2213,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1987,10 +2251,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2013,9 +2277,11 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L13" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2066,7 +2332,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2086,10 +2352,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2112,9 +2378,11 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L14" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2165,7 +2433,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2185,10 +2453,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2211,9 +2479,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="L15" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2264,7 +2534,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2279,6 +2549,3036 @@
         <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y19" s="2"/>
+      <c r="Z19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y25" s="2"/>
+      <c r="Z25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="223">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,10 @@
     <t>InfrastructureRoot.typeId</t>
   </si>
   <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
+  </si>
+  <si>
     <t>Performer1.typeId.nullFlavor</t>
   </si>
   <si>
@@ -470,6 +474,34 @@
   </si>
   <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant</t>
   </si>
   <si>
     <t>Performer1.assignedEntity.sdtcIdentifiedBy</t>
@@ -976,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.046875" customWidth="true" bestFit="true"/>
@@ -1530,7 +1562,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1538,10 +1570,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1639,17 +1671,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1667,11 +1699,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1722,7 +1754,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1742,17 +1774,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1770,11 +1802,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1825,7 +1857,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1845,17 +1877,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1873,11 +1905,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1928,7 +1960,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1948,17 +1980,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1976,11 +2008,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2031,7 +2063,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2051,10 +2083,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2081,7 +2113,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2132,7 +2164,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2152,10 +2184,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2181,7 +2213,7 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2213,7 +2245,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2231,7 +2263,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2251,10 +2283,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2277,10 +2309,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2332,7 +2364,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2352,10 +2384,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2378,10 +2410,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2433,7 +2465,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2453,10 +2485,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2479,10 +2511,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2534,7 +2566,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2554,10 +2586,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2655,10 +2687,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2756,10 +2788,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2849,7 +2881,7 @@
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2857,10 +2889,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2958,17 +2990,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2986,11 +3018,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3041,7 +3073,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3061,17 +3093,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -3089,11 +3121,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3144,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3164,17 +3196,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>75</v>
@@ -3192,11 +3224,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3205,7 +3237,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>74</v>
@@ -3247,7 +3279,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3267,17 +3299,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>75</v>
@@ -3295,11 +3327,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3350,7 +3382,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3370,10 +3402,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3400,7 +3432,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3451,7 +3483,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3471,10 +3503,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3508,7 +3540,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3530,7 +3562,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3548,7 +3580,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3568,10 +3600,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3647,7 +3679,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3667,16 +3699,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
@@ -3693,10 +3727,12 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3722,13 +3758,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3746,13 +3780,13 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
@@ -3766,21 +3800,23 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E28" s="2"/>
+      <c r="E28" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3792,10 +3828,12 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3821,11 +3859,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3843,7 +3883,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3863,17 +3903,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -3891,11 +3931,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3922,11 +3962,13 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -3944,7 +3986,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3964,20 +4006,20 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
@@ -3992,11 +4034,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="M30" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4047,7 +4091,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4067,20 +4111,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4095,11 +4139,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="M31" t="s" s="2">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4150,7 +4196,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4170,23 +4216,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E32" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4198,12 +4242,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="L32" s="2"/>
-      <c r="M32" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4253,13 +4295,13 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
@@ -4273,23 +4315,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E33" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -4301,12 +4341,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="L33" s="2"/>
-      <c r="M33" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4332,13 +4370,11 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4356,7 +4392,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4376,23 +4412,23 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>74</v>
@@ -4404,11 +4440,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4435,13 +4471,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4459,7 +4493,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4479,21 +4513,23 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4505,11 +4541,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4560,7 +4596,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4580,21 +4616,23 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4606,11 +4644,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4661,7 +4699,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4681,17 +4719,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4709,11 +4747,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4764,7 +4802,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4784,17 +4822,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4812,11 +4850,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4867,13 +4905,13 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
@@ -4887,23 +4925,23 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -4915,11 +4953,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4970,13 +5008,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -4990,10 +5028,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5004,7 +5042,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5016,10 +5054,12 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="M40" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5069,13 +5109,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5089,10 +5129,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5103,7 +5143,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5115,10 +5155,12 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
+      <c r="M41" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5168,13 +5210,13 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
@@ -5188,16 +5230,18 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5214,10 +5258,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5267,7 +5313,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5287,21 +5333,23 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5313,10 +5361,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5366,13 +5416,13 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>74</v>
@@ -5386,21 +5436,23 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -5412,10 +5464,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5465,13 +5519,13 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>74</v>
@@ -5485,10 +5539,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,10 +5550,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5511,7 +5565,7 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -5564,21 +5618,516 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="229">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>Performer1.assignedEntity.id</t>
+  </si>
+  <si>
+    <t>Identifiant du responsable</t>
   </si>
   <si>
     <t>AssignedEntity.id</t>
@@ -501,7 +504,9 @@
     <t>Performer1.assignedEntity.id.extension</t>
   </si>
   <si>
-    <t>Valeur de l’identifiant</t>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>Performer1.assignedEntity.sdtcIdentifiedBy</t>
@@ -517,6 +522,9 @@
     <t>Performer1.assignedEntity.code</t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -660,6 +668,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -670,6 +681,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -680,6 +694,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -688,6 +709,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -3628,7 +3654,9 @@
       <c r="K26" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L26" s="2"/>
+      <c r="L26" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3679,7 +3707,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3699,10 +3727,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3800,10 +3828,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3903,10 +3931,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4006,10 +4034,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4037,10 +4065,10 @@
         <v>112</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4111,10 +4139,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4142,7 +4170,7 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>118</v>
@@ -4216,10 +4244,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4242,7 +4270,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -4295,7 +4323,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4315,10 +4343,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4343,7 +4371,9 @@
       <c r="K33" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4374,7 +4404,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4392,7 +4422,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4412,10 +4442,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4513,10 +4543,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4545,7 +4575,7 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4596,7 +4626,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4616,17 +4646,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4648,7 +4678,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4699,7 +4729,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4719,17 +4749,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4751,7 +4781,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4802,7 +4832,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4822,17 +4852,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4854,7 +4884,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4905,7 +4935,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4925,17 +4955,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -4957,7 +4987,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5008,7 +5038,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5028,10 +5058,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5054,11 +5084,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5109,7 +5139,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5129,10 +5159,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5159,7 +5189,7 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5210,7 +5240,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5230,17 +5260,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
@@ -5258,11 +5288,11 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5313,7 +5343,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5333,17 +5363,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5361,11 +5391,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5416,7 +5446,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5436,17 +5466,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5464,11 +5494,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5519,7 +5549,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5539,10 +5569,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5565,9 +5595,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5618,7 +5650,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5638,10 +5670,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5664,9 +5696,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5717,7 +5751,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5737,10 +5771,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5763,9 +5797,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5816,7 +5852,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5836,10 +5872,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5862,9 +5898,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5915,7 +5953,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5935,10 +5973,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5961,7 +5999,7 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6014,7 +6052,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6034,10 +6072,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6113,7 +6151,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Performer est l'exécutant de l’évènement documenté. Il est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal.</t>
+    <t>L'élément de l'en-tête du CDA performer permet de représenter l'exécutant de l’évènement documenté. Il est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
